--- a/data/satisfaction_detail/2026/6月/商务简餐.xlsx
+++ b/data/satisfaction_detail/2026/6月/商务简餐.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>9.98</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>9.890000000000001</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>10</v>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.33</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="15">
